--- a/MATLAB Files/tests.xlsx
+++ b/MATLAB Files/tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saima\Desktop\FYP\collab\FYP_Non_contact_radar\MATLAB Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018F7DAE-16C0-4D64-A89B-C66E36948A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D210C048-B2A0-4C0A-8DF3-616885A80B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="280" windowWidth="19200" windowHeight="11720" xr2:uid="{031E787E-2CC5-4268-83A1-4B4C9EA53E11}"/>
   </bookViews>
@@ -613,37 +613,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1253,16 +1222,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>20131</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>51392</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>406399</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>158749</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>566894</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19189</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
